--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -119,6 +119,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -486,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X4"/>
+  <dimension ref="A1:X5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -707,7 +711,9 @@
       <c r="U2" s="9" t="n">
         <v/>
       </c>
-      <c r="V2" s="6" t="inlineStr"/>
+      <c r="V2" s="9" t="n">
+        <v/>
+      </c>
       <c r="W2" s="10" t="inlineStr">
         <is>
           <t>空方</t>
@@ -789,7 +795,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V3" s="6" t="inlineStr"/>
+      <c r="V3" s="9" t="n">
+        <v/>
+      </c>
       <c r="W3" s="10" t="inlineStr">
         <is>
           <t>空方</t>
@@ -802,31 +810,113 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="C4" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="D4" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="E4" t="n">
+        <v>108.15</v>
+      </c>
+      <c r="F4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I4" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>104.37</v>
+      </c>
+      <c r="K4" t="n">
+        <v>105.35</v>
+      </c>
+      <c r="L4" t="n">
+        <v>106.32</v>
+      </c>
+      <c r="M4" t="n">
+        <v>106.75</v>
+      </c>
+      <c r="N4" t="n">
+        <v>107.17</v>
+      </c>
+      <c r="O4" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr"/>
+      <c r="Q4" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W4" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I4" s="12" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="J4" s="12" t="n">
-        <v>104.37</v>
-      </c>
-      <c r="K4" s="12" t="n">
-        <v>105.35</v>
-      </c>
-      <c r="L4" s="12" t="n">
-        <v>106.32</v>
-      </c>
-      <c r="M4" s="12" t="n">
+      <c r="I5" s="14" t="n">
         <v>106.75</v>
       </c>
-      <c r="N4" s="12" t="n">
-        <v>107.17</v>
-      </c>
-      <c r="O4" s="12" t="n">
-        <v>108.7</v>
+      <c r="J5" s="14" t="n">
+        <v>107.28</v>
+      </c>
+      <c r="K5" s="14" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="L5" s="14" t="n">
+        <v>108.12</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>109.07</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>109.45</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107.65</v>
+        <v>108.45</v>
       </c>
       <c r="C4" t="n">
-        <v>108.55</v>
+        <v>109.6</v>
       </c>
       <c r="D4" t="n">
         <v>107.65</v>
@@ -834,7 +834,7 @@
         <v>0.0198</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>1.95</v>
       </c>
       <c r="I4" t="n">
         <v>104.5</v>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>106.75</v>
+        <v>105.7</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>107.28</v>
+        <v>105.96</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>107.7</v>
+        <v>107.18</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>108.12</v>
+        <v>108.39</v>
       </c>
       <c r="M5" s="14" t="n">
-        <v>108.6</v>
+        <v>109.12</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>109.07</v>
+        <v>109.86</v>
       </c>
       <c r="O5" s="14" t="n">
-        <v>109.45</v>
+        <v>111.55</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -654,19 +654,19 @@
         <v>107.15</v>
       </c>
       <c r="D2" t="n">
-        <v>105.95</v>
+        <v>105.9</v>
       </c>
       <c r="E2" t="n">
-        <v>106.2</v>
+        <v>106.05</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.45</v>
+        <v>-2.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0225</v>
+        <v>-0.0239</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="I2" t="n">
         <v>102.95</v>
@@ -732,46 +732,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>106.25</v>
+        <v>106.75</v>
       </c>
       <c r="C3" t="n">
-        <v>107.3</v>
+        <v>108.55</v>
       </c>
       <c r="D3" t="n">
-        <v>105.9</v>
+        <v>106.6</v>
       </c>
       <c r="E3" t="n">
-        <v>106.05</v>
+        <v>108.15</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.15</v>
+        <v>2.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0014</v>
+        <v>0.0198</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="I3" t="n">
-        <v>104.75</v>
+        <v>104.65</v>
       </c>
       <c r="J3" t="n">
-        <v>104.82</v>
+        <v>104.56</v>
       </c>
       <c r="K3" t="n">
-        <v>105.6</v>
+        <v>105.42</v>
       </c>
       <c r="L3" t="n">
-        <v>106.38</v>
+        <v>106.29</v>
       </c>
       <c r="M3" t="n">
-        <v>106.8</v>
+        <v>106.67</v>
       </c>
       <c r="N3" t="n">
-        <v>107.22</v>
+        <v>107.06</v>
       </c>
       <c r="O3" t="n">
-        <v>108.35</v>
+        <v>108.4</v>
       </c>
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="7" t="n">
@@ -780,9 +780,9 @@
       <c r="R3" s="7" t="n">
         <v/>
       </c>
-      <c r="S3" s="8" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S3" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="9" t="inlineStr">
@@ -795,19 +795,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V3" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W3" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="V3" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W3" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -819,43 +817,43 @@
         <v>108.45</v>
       </c>
       <c r="C4" t="n">
-        <v>109.6</v>
+        <v>109.9</v>
       </c>
       <c r="D4" t="n">
-        <v>107.65</v>
+        <v>108.1</v>
       </c>
       <c r="E4" t="n">
-        <v>108.15</v>
+        <v>109.9</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0198</v>
+        <v>0.0162</v>
       </c>
       <c r="H4" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="I4" t="n">
-        <v>104.5</v>
+        <v>104.65</v>
       </c>
       <c r="J4" t="n">
-        <v>104.37</v>
+        <v>106.49</v>
       </c>
       <c r="K4" t="n">
-        <v>105.35</v>
+        <v>107.17</v>
       </c>
       <c r="L4" t="n">
-        <v>106.32</v>
+        <v>107.86</v>
       </c>
       <c r="M4" t="n">
-        <v>106.75</v>
+        <v>109.12</v>
       </c>
       <c r="N4" t="n">
-        <v>107.17</v>
+        <v>110.39</v>
       </c>
       <c r="O4" t="n">
-        <v>108.7</v>
+        <v>110.5</v>
       </c>
       <c r="P4" s="6" t="inlineStr"/>
       <c r="Q4" s="7" t="n">
@@ -876,13 +874,11 @@
       </c>
       <c r="U4" s="9" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V4" s="9" t="n">
+        <v/>
       </c>
       <c r="W4" s="12" t="inlineStr">
         <is>
@@ -898,25 +894,25 @@
         </is>
       </c>
       <c r="I5" s="14" t="n">
-        <v>105.7</v>
+        <v>106.3</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>105.96</v>
+        <v>108.55</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>107.18</v>
+        <v>109</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>108.39</v>
+        <v>109.45</v>
       </c>
       <c r="M5" s="14" t="n">
-        <v>109.12</v>
+        <v>110.8</v>
       </c>
       <c r="N5" s="14" t="n">
-        <v>109.86</v>
+        <v>112.15</v>
       </c>
       <c r="O5" s="14" t="n">
-        <v>111.55</v>
+        <v>111.7</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,8 +118,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -888,32 +881,82 @@
       <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="n">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="C5" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="D5" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="E5" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I5" t="n">
         <v>106.3</v>
       </c>
-      <c r="J5" s="14" t="n">
+      <c r="J5" t="n">
         <v>108.55</v>
       </c>
-      <c r="K5" s="14" t="n">
+      <c r="K5" t="n">
         <v>109</v>
       </c>
-      <c r="L5" s="14" t="n">
+      <c r="L5" t="n">
         <v>109.45</v>
       </c>
-      <c r="M5" s="14" t="n">
+      <c r="M5" t="n">
         <v>110.8</v>
       </c>
-      <c r="N5" s="14" t="n">
+      <c r="N5" t="n">
         <v>112.15</v>
       </c>
-      <c r="O5" s="14" t="n">
+      <c r="O5" t="n">
         <v>111.7</v>
       </c>
+      <c r="P5" s="6" t="inlineStr"/>
+      <c r="Q5" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -887,25 +887,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>108.85</v>
+        <v>109.8</v>
       </c>
       <c r="C5" t="n">
-        <v>109.9</v>
+        <v>110.45</v>
       </c>
       <c r="D5" t="n">
-        <v>108.85</v>
+        <v>109.25</v>
       </c>
       <c r="E5" t="n">
-        <v>109.9</v>
+        <v>110.35</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0</v>
+        <v>0.0041</v>
       </c>
       <c r="H5" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="I5" t="n">
         <v>106.3</v>
@@ -932,18 +932,18 @@
       <c r="Q5" s="7" t="n">
         <v/>
       </c>
-      <c r="R5" s="7" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="7" t="n">
+        <v/>
       </c>
       <c r="S5" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="9" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="9" t="n">
         <v/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X5"/>
+  <dimension ref="A1:X6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -958,6 +958,88 @@
       </c>
       <c r="X5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="C6" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>110.45</v>
+      </c>
+      <c r="E6" t="n">
+        <v>114.05</v>
+      </c>
+      <c r="F6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.0335</v>
+      </c>
+      <c r="H6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I6" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="J6" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>110.1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="N6" t="n">
+        <v>111.8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>111.65</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr"/>
+      <c r="Q6" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V6" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W6" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X6"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1040,6 +1040,88 @@
       </c>
       <c r="X6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>114.35</v>
+      </c>
+      <c r="C7" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="J7" t="n">
+        <v>111.29</v>
+      </c>
+      <c r="K7" t="n">
+        <v>112.22</v>
+      </c>
+      <c r="L7" t="n">
+        <v>113.16</v>
+      </c>
+      <c r="M7" t="n">
+        <v>115.87</v>
+      </c>
+      <c r="N7" t="n">
+        <v>118.59</v>
+      </c>
+      <c r="O7" t="n">
+        <v>117.75</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
+      <c r="Q7" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -1056,13 +1056,13 @@
         <v>112.2</v>
       </c>
       <c r="E7" t="n">
-        <v>112.6</v>
+        <v>113.55</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.45</v>
+        <v>-0.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.0044</v>
       </c>
       <c r="H7" t="n">
         <v>2.2</v>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="R7" s="7" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="9" t="n">

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:X8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1122,6 +1122,86 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="C8" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>110</v>
+      </c>
+      <c r="J8" t="n">
+        <v>111.48</v>
+      </c>
+      <c r="K8" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="L8" t="n">
+        <v>113.43</v>
+      </c>
+      <c r="M8" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="N8" t="n">
+        <v>115.88</v>
+      </c>
+      <c r="O8" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr"/>
+      <c r="Q8" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -1129,25 +1129,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>112.55</v>
+        <v>113.45</v>
       </c>
       <c r="C8" t="n">
-        <v>113.7</v>
+        <v>113.65</v>
       </c>
       <c r="D8" t="n">
-        <v>112.5</v>
+        <v>112.9</v>
       </c>
       <c r="E8" t="n">
-        <v>113.55</v>
+        <v>113.05</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0</v>
+        <v>-0.0044</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2</v>
+        <v>0.75</v>
       </c>
       <c r="I8" t="n">
         <v>110</v>
@@ -1177,9 +1177,9 @@
       <c r="R8" s="7" t="n">
         <v/>
       </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S8" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="9" t="n">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -1135,19 +1135,19 @@
         <v>113.65</v>
       </c>
       <c r="D8" t="n">
-        <v>112.9</v>
+        <v>112.3</v>
       </c>
       <c r="E8" t="n">
-        <v>113.05</v>
+        <v>112.65</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.75</v>
+        <v>1.35</v>
       </c>
       <c r="I8" t="n">
         <v>110</v>
@@ -1174,12 +1174,14 @@
       <c r="Q8" s="7" t="n">
         <v/>
       </c>
-      <c r="R8" s="7" t="n">
-        <v/>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="8" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="9" t="n">

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X8"/>
+  <dimension ref="A1:X9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1204,6 +1204,86 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="D9" t="n">
+        <v>112.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.0013</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="I9" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>111.14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>111.97</v>
+      </c>
+      <c r="L9" t="n">
+        <v>112.81</v>
+      </c>
+      <c r="M9" t="n">
+        <v>113.33</v>
+      </c>
+      <c r="N9" t="n">
+        <v>113.84</v>
+      </c>
+      <c r="O9" t="n">
+        <v>115</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr"/>
+      <c r="Q9" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X9"/>
+  <dimension ref="A1:X10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1284,6 +1284,90 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>112.05</v>
+      </c>
+      <c r="E10" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-0.0013</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="J10" t="n">
+        <v>112.16</v>
+      </c>
+      <c r="K10" t="n">
+        <v>112.42</v>
+      </c>
+      <c r="L10" t="n">
+        <v>112.69</v>
+      </c>
+      <c r="M10" t="n">
+        <v>113.17</v>
+      </c>
+      <c r="N10" t="n">
+        <v>113.66</v>
+      </c>
+      <c r="O10" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X10"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1368,6 +1368,92 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="C11" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="D11" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="E11" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.0049</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>111</v>
+      </c>
+      <c r="J11" t="n">
+        <v>111.64</v>
+      </c>
+      <c r="K11" t="n">
+        <v>112.12</v>
+      </c>
+      <c r="L11" t="n">
+        <v>112.61</v>
+      </c>
+      <c r="M11" t="n">
+        <v>113.17</v>
+      </c>
+      <c r="N11" t="n">
+        <v>113.74</v>
+      </c>
+      <c r="O11" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X11"/>
+  <dimension ref="A1:X12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1454,6 +1454,86 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>113.45</v>
+      </c>
+      <c r="D12" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="E12" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="J12" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="K12" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="L12" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="M12" t="n">
+        <v>114.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="O12" t="n">
+        <v>115.65</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr"/>
+      <c r="Q12" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1534,6 +1534,90 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="C13" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="D13" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.0031</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>111.45</v>
+      </c>
+      <c r="J13" t="n">
+        <v>111.88</v>
+      </c>
+      <c r="K13" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>112.93</v>
+      </c>
+      <c r="M13" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>113.88</v>
+      </c>
+      <c r="O13" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr"/>
+      <c r="Q13" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X13"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1618,6 +1618,86 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>113.55</v>
+      </c>
+      <c r="D14" t="n">
+        <v>112.95</v>
+      </c>
+      <c r="E14" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.0004</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I14" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="J14" t="n">
+        <v>112.18</v>
+      </c>
+      <c r="K14" t="n">
+        <v>112.65</v>
+      </c>
+      <c r="L14" t="n">
+        <v>113.12</v>
+      </c>
+      <c r="M14" t="n">
+        <v>113.85</v>
+      </c>
+      <c r="N14" t="n">
+        <v>114.57</v>
+      </c>
+      <c r="O14" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr"/>
+      <c r="Q14" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X14"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1698,6 +1698,88 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="C15" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="D15" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>117.3</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I15" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="J15" t="n">
+        <v>112.73</v>
+      </c>
+      <c r="K15" t="n">
+        <v>113</v>
+      </c>
+      <c r="L15" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="M15" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="N15" t="n">
+        <v>113.93</v>
+      </c>
+      <c r="O15" t="n">
+        <v>114.15</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr"/>
+      <c r="Q15" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="9" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W15" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1780,6 +1780,166 @@
       </c>
       <c r="X15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="C16" t="n">
+        <v>117.65</v>
+      </c>
+      <c r="D16" t="n">
+        <v>116.2</v>
+      </c>
+      <c r="E16" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I16" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>115.47</v>
+      </c>
+      <c r="K16" t="n">
+        <v>116.15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>116.82</v>
+      </c>
+      <c r="M16" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="N16" t="n">
+        <v>120.07</v>
+      </c>
+      <c r="O16" t="n">
+        <v>119.8</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr"/>
+      <c r="Q16" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>117.1</v>
+      </c>
+      <c r="C17" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>116.95</v>
+      </c>
+      <c r="E17" t="n">
+        <v>117.05</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I17" t="n">
+        <v>114.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>115.66</v>
+      </c>
+      <c r="K17" t="n">
+        <v>116.33</v>
+      </c>
+      <c r="L17" t="n">
+        <v>116.99</v>
+      </c>
+      <c r="M17" t="n">
+        <v>117.78</v>
+      </c>
+      <c r="N17" t="n">
+        <v>118.56</v>
+      </c>
+      <c r="O17" t="n">
+        <v>119.1</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr"/>
+      <c r="Q17" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1870,22 +1870,22 @@
         <v>117.1</v>
       </c>
       <c r="C17" t="n">
-        <v>117.5</v>
+        <v>117.1</v>
       </c>
       <c r="D17" t="n">
-        <v>116.95</v>
+        <v>115</v>
       </c>
       <c r="E17" t="n">
-        <v>117.05</v>
+        <v>115.7</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-1.35</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0</v>
+        <v>-0.0115</v>
       </c>
       <c r="H17" t="n">
-        <v>0.55</v>
+        <v>2.1</v>
       </c>
       <c r="I17" t="n">
         <v>114.75</v>
@@ -1909,15 +1909,19 @@
         <v>119.1</v>
       </c>
       <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="9" t="n">
@@ -1935,6 +1939,86 @@
         </is>
       </c>
       <c r="X17" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>116</v>
+      </c>
+      <c r="C18" t="n">
+        <v>116.05</v>
+      </c>
+      <c r="D18" t="n">
+        <v>115</v>
+      </c>
+      <c r="E18" t="n">
+        <v>115.7</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I18" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>113.43</v>
+      </c>
+      <c r="K18" t="n">
+        <v>114.65</v>
+      </c>
+      <c r="L18" t="n">
+        <v>115.88</v>
+      </c>
+      <c r="M18" t="n">
+        <v>116.75</v>
+      </c>
+      <c r="N18" t="n">
+        <v>117.62</v>
+      </c>
+      <c r="O18" t="n">
+        <v>119.2</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr"/>
+      <c r="Q18" s="7" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="7" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="12" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -1951,25 +1951,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>116</v>
+        <v>115.5</v>
       </c>
       <c r="C18" t="n">
-        <v>116.05</v>
+        <v>115.85</v>
       </c>
       <c r="D18" t="n">
-        <v>115</v>
+        <v>114.9</v>
       </c>
       <c r="E18" t="n">
-        <v>115.7</v>
+        <v>114.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0</v>
+        <v>-0.0069</v>
       </c>
       <c r="H18" t="n">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
       <c r="I18" t="n">
         <v>112.9</v>
@@ -1996,12 +1996,14 @@
       <c r="Q18" s="7" t="n">
         <v/>
       </c>
-      <c r="R18" s="7" t="n">
-        <v/>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="9" t="n">
@@ -2020,7 +2022,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -101,9 +101,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -682,32 +679,34 @@
       <c r="O2" t="n">
         <v>111.65</v>
       </c>
-      <c r="P2" s="6" t="inlineStr"/>
-      <c r="Q2" s="7" t="inlineStr">
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="7" t="inlineStr">
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W2" s="10" t="inlineStr">
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W2" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -766,34 +765,36 @@
       <c r="O3" t="n">
         <v>108.4</v>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="11" t="inlineStr">
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T3" s="9" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="9" t="inlineStr">
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V3" s="9" t="inlineStr">
+      <c r="V3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W3" s="12" t="inlineStr">
+      <c r="W3" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -848,32 +849,34 @@
       <c r="O4" t="n">
         <v>110.5</v>
       </c>
-      <c r="P4" s="6" t="inlineStr"/>
-      <c r="Q4" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T4" s="9" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="9" t="inlineStr">
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V4" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="12" t="inlineStr">
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -928,30 +931,32 @@
       <c r="O5" t="n">
         <v>111.7</v>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
-      <c r="Q5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T5" s="9" t="inlineStr">
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="12" t="inlineStr">
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1006,34 +1011,36 @@
       <c r="O6" t="n">
         <v>111.65</v>
       </c>
-      <c r="P6" s="6" t="inlineStr"/>
-      <c r="Q6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T6" s="9" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="9" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V6" s="9" t="inlineStr">
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W6" s="12" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1088,30 +1095,32 @@
       <c r="O7" t="n">
         <v>117.75</v>
       </c>
-      <c r="P7" s="6" t="inlineStr"/>
-      <c r="Q7" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="7" t="inlineStr">
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="11" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="12" t="inlineStr">
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1170,30 +1179,32 @@
       <c r="O8" t="n">
         <v>116.6</v>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
-      <c r="Q8" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="7" t="inlineStr">
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="12" t="inlineStr">
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1252,28 +1263,30 @@
       <c r="O9" t="n">
         <v>115</v>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
-      <c r="Q9" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="12" t="inlineStr">
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1332,32 +1345,34 @@
       <c r="O10" t="n">
         <v>113.7</v>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
-      <c r="Q10" s="7" t="inlineStr">
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R10" s="7" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="12" t="inlineStr">
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1416,34 +1431,36 @@
       <c r="O11" t="n">
         <v>114.15</v>
       </c>
-      <c r="P11" s="6" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr">
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R11" s="7" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T11" s="9" t="inlineStr">
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="12" t="inlineStr">
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1502,28 +1519,30 @@
       <c r="O12" t="n">
         <v>115.65</v>
       </c>
-      <c r="P12" s="6" t="inlineStr"/>
-      <c r="Q12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="11" t="inlineStr">
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="12" t="inlineStr">
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1582,32 +1601,34 @@
       <c r="O13" t="n">
         <v>114.45</v>
       </c>
-      <c r="P13" s="6" t="inlineStr"/>
-      <c r="Q13" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="7" t="inlineStr">
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="11" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T13" s="9" t="inlineStr">
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="12" t="inlineStr">
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1666,28 +1687,30 @@
       <c r="O14" t="n">
         <v>114.8</v>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
-      <c r="Q14" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="12" t="inlineStr">
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1746,34 +1769,36 @@
       <c r="O15" t="n">
         <v>114.15</v>
       </c>
-      <c r="P15" s="6" t="inlineStr"/>
-      <c r="Q15" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T15" s="9" t="inlineStr">
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="9" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V15" s="9" t="inlineStr">
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W15" s="12" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1828,28 +1853,30 @@
       <c r="O16" t="n">
         <v>119.8</v>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
-      <c r="Q16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="7" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="11" t="inlineStr">
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="12" t="inlineStr">
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1908,32 +1935,34 @@
       <c r="O17" t="n">
         <v>119.1</v>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
-      <c r="Q17" s="7" t="inlineStr">
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="12" t="inlineStr">
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1992,30 +2021,32 @@
       <c r="O18" t="n">
         <v>119.2</v>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
-      <c r="Q18" s="7" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="7" t="inlineStr">
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="9" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="12" t="inlineStr">
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2025,6 +2056,90 @@
           <t>強警訊</t>
         </is>
       </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="C19" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="D19" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="E19" t="n">
+        <v>113.6</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.0113</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I19" t="n">
+        <v>113.95</v>
+      </c>
+      <c r="J19" t="n">
+        <v>113.71</v>
+      </c>
+      <c r="K19" t="n">
+        <v>114.43</v>
+      </c>
+      <c r="L19" t="n">
+        <v>115.14</v>
+      </c>
+      <c r="M19" t="n">
+        <v>115.38</v>
+      </c>
+      <c r="N19" t="n">
+        <v>115.61</v>
+      </c>
+      <c r="O19" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2064,25 +2064,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>114.2</v>
+        <v>113.6</v>
       </c>
       <c r="C19" t="n">
-        <v>114.7</v>
+        <v>115.2</v>
       </c>
       <c r="D19" t="n">
-        <v>112.9</v>
+        <v>113.6</v>
       </c>
       <c r="E19" t="n">
-        <v>113.6</v>
+        <v>113.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0113</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I19" t="n">
         <v>113.95</v>
@@ -2134,12 +2134,100 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="C20" t="n">
+        <v>114.7</v>
+      </c>
+      <c r="D20" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="E20" t="n">
+        <v>113.8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I20" t="n">
+        <v>112</v>
+      </c>
+      <c r="J20" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>113</v>
+      </c>
+      <c r="L20" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>114.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2152,25 +2152,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>114.7</v>
+        <v>113.5</v>
       </c>
       <c r="C20" t="n">
-        <v>114.7</v>
+        <v>113.5</v>
       </c>
       <c r="D20" t="n">
-        <v>113.8</v>
+        <v>112.1</v>
       </c>
       <c r="E20" t="n">
-        <v>113.8</v>
+        <v>113.3</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0</v>
+        <v>-0.0044</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I20" t="n">
         <v>112</v>
@@ -2199,31 +2199,115 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="C21" t="n">
+        <v>113.35</v>
+      </c>
+      <c r="D21" t="n">
+        <v>112.35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="J21" t="n">
+        <v>112.15</v>
+      </c>
+      <c r="K21" t="n">
+        <v>112.6</v>
+      </c>
+      <c r="L21" t="n">
+        <v>113.05</v>
+      </c>
+      <c r="M21" t="n">
+        <v>114</v>
+      </c>
+      <c r="N21" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="O21" t="n">
+        <v>114.9</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:X22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2236,25 +2236,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>112.8</v>
+        <v>113.45</v>
       </c>
       <c r="C21" t="n">
-        <v>113.35</v>
+        <v>114</v>
       </c>
       <c r="D21" t="n">
-        <v>112.35</v>
+        <v>111.2</v>
       </c>
       <c r="E21" t="n">
-        <v>113.3</v>
+        <v>111.35</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-1.95</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0</v>
+        <v>-0.0172</v>
       </c>
       <c r="H21" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="I21" t="n">
         <v>110.7</v>
@@ -2277,24 +2277,30 @@
       <c r="O21" t="n">
         <v>114.9</v>
       </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2302,9 +2308,9 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -2312,6 +2318,86 @@
           <t>弱警訊</t>
         </is>
       </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="C22" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="D22" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>111.35</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="J22" t="n">
+        <v>107.92</v>
+      </c>
+      <c r="K22" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="L22" t="n">
+        <v>111.97</v>
+      </c>
+      <c r="M22" t="n">
+        <v>112.75</v>
+      </c>
+      <c r="N22" t="n">
+        <v>113.52</v>
+      </c>
+      <c r="O22" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:X23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2326,25 +2326,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>113.25</v>
+        <v>110.6</v>
       </c>
       <c r="C22" t="n">
-        <v>113.4</v>
+        <v>110.6</v>
       </c>
       <c r="D22" t="n">
-        <v>111.2</v>
+        <v>107.1</v>
       </c>
       <c r="E22" t="n">
-        <v>111.35</v>
+        <v>109.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-1.95</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0</v>
+        <v>-0.0175</v>
       </c>
       <c r="H22" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="I22" t="n">
         <v>108.4</v>
@@ -2367,37 +2367,121 @@
       <c r="O22" t="n">
         <v>116.8</v>
       </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>108.85</v>
+      </c>
+      <c r="C23" t="n">
+        <v>109.6</v>
+      </c>
+      <c r="D23" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>106.18</v>
+      </c>
+      <c r="K23" t="n">
+        <v>107.65</v>
+      </c>
+      <c r="L23" t="n">
+        <v>109.12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="N23" t="n">
+        <v>113.18</v>
+      </c>
+      <c r="O23" t="n">
+        <v>114.1</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -2410,25 +2410,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>108.85</v>
+        <v>109.15</v>
       </c>
       <c r="C23" t="n">
-        <v>109.6</v>
+        <v>109.8</v>
       </c>
       <c r="D23" t="n">
-        <v>107.1</v>
+        <v>108.95</v>
       </c>
       <c r="E23" t="n">
-        <v>109.4</v>
+        <v>109.2</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0</v>
+        <v>-0.0018</v>
       </c>
       <c r="H23" t="n">
-        <v>2.5</v>
+        <v>0.85</v>
       </c>
       <c r="I23" t="n">
         <v>103.6</v>
@@ -2457,10 +2457,8 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
@@ -2481,7 +2479,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:X24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2485,6 +2485,90 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>109.15</v>
+      </c>
+      <c r="C24" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="E24" t="n">
+        <v>106.55</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-2.65</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>-0.0243</v>
+      </c>
+      <c r="H24" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I24" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>108.26</v>
+      </c>
+      <c r="K24" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="L24" t="n">
+        <v>109.29</v>
+      </c>
+      <c r="M24" t="n">
+        <v>109.62</v>
+      </c>
+      <c r="N24" t="n">
+        <v>109.96</v>
+      </c>
+      <c r="O24" t="n">
+        <v>110.65</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:X25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2492,25 +2492,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>109.15</v>
+        <v>106.8</v>
       </c>
       <c r="C24" t="n">
-        <v>109.2</v>
+        <v>109</v>
       </c>
       <c r="D24" t="n">
-        <v>106.25</v>
+        <v>106.75</v>
       </c>
       <c r="E24" t="n">
-        <v>106.55</v>
+        <v>108.35</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.65</v>
+        <v>-0.85</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0243</v>
+        <v>-0.0078</v>
       </c>
       <c r="H24" t="n">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="I24" t="n">
         <v>108.1</v>
@@ -2535,19 +2535,19 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2568,6 +2568,88 @@
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="C25" t="n">
+        <v>109</v>
+      </c>
+      <c r="D25" t="n">
+        <v>108.05</v>
+      </c>
+      <c r="E25" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I25" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="K25" t="n">
+        <v>107.22</v>
+      </c>
+      <c r="L25" t="n">
+        <v>108.11</v>
+      </c>
+      <c r="M25" t="n">
+        <v>109.47</v>
+      </c>
+      <c r="N25" t="n">
+        <v>110.84</v>
+      </c>
+      <c r="O25" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:X26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2576,25 +2576,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>108.1</v>
+        <v>107.8</v>
       </c>
       <c r="C25" t="n">
-        <v>109</v>
+        <v>108.95</v>
       </c>
       <c r="D25" t="n">
-        <v>108.05</v>
+        <v>106.95</v>
       </c>
       <c r="E25" t="n">
-        <v>108.35</v>
+        <v>108.75</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0</v>
+        <v>0.0037</v>
       </c>
       <c r="H25" t="n">
-        <v>0.95</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
         <v>104.5</v>
@@ -2623,8 +2623,10 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
@@ -2647,9 +2649,91 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>108.95</v>
+      </c>
+      <c r="D26" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="E26" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="J26" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="K26" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="L26" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="M26" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="N26" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="O26" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:X27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2735,6 +2735,90 @@
       </c>
       <c r="X26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>109.05</v>
+      </c>
+      <c r="C27" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="D27" t="n">
+        <v>109</v>
+      </c>
+      <c r="E27" t="n">
+        <v>110</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I27" t="n">
+        <v>104.95</v>
+      </c>
+      <c r="J27" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="K27" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="L27" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="M27" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="N27" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="O27" t="n">
+        <v>110.95</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -2660,25 +2660,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>107.3</v>
+        <v>109.4</v>
       </c>
       <c r="C26" t="n">
-        <v>108.95</v>
+        <v>110.05</v>
       </c>
       <c r="D26" t="n">
-        <v>106.95</v>
+        <v>108.15</v>
       </c>
       <c r="E26" t="n">
-        <v>108.75</v>
+        <v>110</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0</v>
+        <v>0.0115</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="I26" t="n">
         <v>104.95</v>
@@ -2704,23 +2704,21 @@
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2733,7 +2731,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2754,34 +2756,34 @@
         <v>110</v>
       </c>
       <c r="F27" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0115</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>1.05</v>
       </c>
       <c r="I27" t="n">
-        <v>104.95</v>
+        <v>106.25</v>
       </c>
       <c r="J27" t="n">
-        <v>107.15</v>
+        <v>108.55</v>
       </c>
       <c r="K27" t="n">
-        <v>107.75</v>
+        <v>109.05</v>
       </c>
       <c r="L27" t="n">
-        <v>108.35</v>
+        <v>109.55</v>
       </c>
       <c r="M27" t="n">
-        <v>109.75</v>
+        <v>110.95</v>
       </c>
       <c r="N27" t="n">
-        <v>111.15</v>
+        <v>112.35</v>
       </c>
       <c r="O27" t="n">
-        <v>110.95</v>
+        <v>111.95</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2789,18 +2791,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2815,7 +2817,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:X28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2744,25 +2744,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>109.05</v>
+        <v>109.35</v>
       </c>
       <c r="C27" t="n">
-        <v>110.05</v>
+        <v>109.75</v>
       </c>
       <c r="D27" t="n">
-        <v>109</v>
+        <v>105.05</v>
       </c>
       <c r="E27" t="n">
-        <v>110</v>
+        <v>105.1</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>-4.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0</v>
+        <v>-0.0445</v>
       </c>
       <c r="H27" t="n">
-        <v>1.05</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
         <v>106.25</v>
@@ -2785,20 +2785,24 @@
       <c r="O27" t="n">
         <v>111.95</v>
       </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2815,11 +2819,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="C28" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D28" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="E28" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="J28" t="n">
+        <v>99.25</v>
+      </c>
+      <c r="K28" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="L28" t="n">
+        <v>106.25</v>
+      </c>
+      <c r="M28" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="N28" t="n">
+        <v>108.65</v>
+      </c>
+      <c r="O28" t="n">
+        <v>114.45</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -2750,19 +2750,19 @@
         <v>109.75</v>
       </c>
       <c r="D27" t="n">
-        <v>105.05</v>
+        <v>106.75</v>
       </c>
       <c r="E27" t="n">
-        <v>105.1</v>
+        <v>106.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.9</v>
+        <v>-3.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0445</v>
+        <v>-0.0291</v>
       </c>
       <c r="H27" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>106.25</v>
@@ -2840,34 +2840,34 @@
         <v>105.1</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>-1.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0</v>
+        <v>-0.0159</v>
       </c>
       <c r="H28" t="n">
         <v>2.1</v>
       </c>
       <c r="I28" t="n">
-        <v>100.35</v>
+        <v>103.75</v>
       </c>
       <c r="J28" t="n">
-        <v>99.25</v>
+        <v>103.08</v>
       </c>
       <c r="K28" t="n">
-        <v>102.75</v>
+        <v>105.3</v>
       </c>
       <c r="L28" t="n">
-        <v>106.25</v>
+        <v>107.53</v>
       </c>
       <c r="M28" t="n">
-        <v>107.45</v>
+        <v>108.3</v>
       </c>
       <c r="N28" t="n">
-        <v>108.65</v>
+        <v>109.08</v>
       </c>
       <c r="O28" t="n">
-        <v>114.45</v>
+        <v>112.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2875,12 +2875,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X28"/>
+  <dimension ref="A1:X29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2901,6 +2901,88 @@
       </c>
       <c r="X28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="C29" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="D29" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="E29" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>102.95</v>
+      </c>
+      <c r="J29" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>104.05</v>
+      </c>
+      <c r="L29" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>106.15</v>
+      </c>
+      <c r="N29" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>109.25</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X29"/>
+  <dimension ref="A1:X30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2908,25 +2908,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>106.65</v>
+        <v>107.1</v>
       </c>
       <c r="C29" t="n">
-        <v>107.15</v>
+        <v>108.4</v>
       </c>
       <c r="D29" t="n">
-        <v>105.05</v>
+        <v>106.1</v>
       </c>
       <c r="E29" t="n">
-        <v>105.1</v>
+        <v>108.3</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0</v>
+        <v>0.0304</v>
       </c>
       <c r="H29" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="I29" t="n">
         <v>102.95</v>
@@ -2958,9 +2958,9 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
@@ -2973,15 +2973,97 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>107.05</v>
+      </c>
+      <c r="C30" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="E30" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I30" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="J30" t="n">
+        <v>106.53</v>
+      </c>
+      <c r="K30" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="L30" t="n">
+        <v>107.78</v>
+      </c>
+      <c r="M30" t="n">
+        <v>109.45</v>
+      </c>
+      <c r="N30" t="n">
+        <v>111.13</v>
+      </c>
+      <c r="O30" t="n">
+        <v>110.7</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X30"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2992,25 +2992,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>107.05</v>
+        <v>108.5</v>
       </c>
       <c r="C30" t="n">
-        <v>108.4</v>
+        <v>109.5</v>
       </c>
       <c r="D30" t="n">
-        <v>106.65</v>
+        <v>108.1</v>
       </c>
       <c r="E30" t="n">
-        <v>108.3</v>
+        <v>108.7</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0</v>
+        <v>0.0037</v>
       </c>
       <c r="H30" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="I30" t="n">
         <v>103.8</v>
@@ -3039,31 +3039,111 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="C31" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="D31" t="n">
+        <v>108.45</v>
+      </c>
+      <c r="E31" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I31" t="n">
+        <v>106.7</v>
+      </c>
+      <c r="J31" t="n">
+        <v>107.25</v>
+      </c>
+      <c r="K31" t="n">
+        <v>108</v>
+      </c>
+      <c r="L31" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="M31" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="N31" t="n">
+        <v>110.05</v>
+      </c>
+      <c r="O31" t="n">
+        <v>110.9</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X31"/>
+  <dimension ref="A1:X32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3075,22 +3075,22 @@
         <v>108.7</v>
       </c>
       <c r="C31" t="n">
-        <v>109.5</v>
+        <v>108.8</v>
       </c>
       <c r="D31" t="n">
-        <v>108.45</v>
+        <v>106.3</v>
       </c>
       <c r="E31" t="n">
-        <v>108.7</v>
+        <v>106.35</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>-2.35</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0</v>
+        <v>-0.0216</v>
       </c>
       <c r="H31" t="n">
-        <v>1.05</v>
+        <v>2.5</v>
       </c>
       <c r="I31" t="n">
         <v>106.7</v>
@@ -3113,37 +3113,121 @@
       <c r="O31" t="n">
         <v>110.9</v>
       </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>107.15</v>
+      </c>
+      <c r="C32" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>106.3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>106.35</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I32" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="J32" t="n">
+        <v>103.25</v>
+      </c>
+      <c r="K32" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="M32" t="n">
+        <v>107.6</v>
+      </c>
+      <c r="N32" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="O32" t="n">
+        <v>111.3</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/T5F_daily.xlsx
+++ b/three_gate/analysis/T5F_daily.xlsx
@@ -3156,25 +3156,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>107.15</v>
+        <v>105.2</v>
       </c>
       <c r="C32" t="n">
-        <v>107.7</v>
+        <v>105.55</v>
       </c>
       <c r="D32" t="n">
-        <v>106.3</v>
+        <v>104</v>
       </c>
       <c r="E32" t="n">
-        <v>106.35</v>
+        <v>104.85</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-1.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0</v>
+        <v>-0.0141</v>
       </c>
       <c r="H32" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="I32" t="n">
         <v>103.8</v>
@@ -3203,18 +3203,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
